--- a/output/extracted_data.xlsx
+++ b/output/extracted_data.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>John</t>
         </is>
       </c>
     </row>
